--- a/projetohotel.lays2B/db/clienteS.xlSx
+++ b/projetohotel.lays2B/db/clienteS.xlSx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -575,6 +575,46 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>2026-05-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>kfrorok</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>929887474</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>kjjjfgr@lfk</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>99804848354</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>wemkremrfrkm</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>kofjejoojfiiore</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>

--- a/projetohotel.lays2B/db/clienteS.xlSx
+++ b/projetohotel.lays2B/db/clienteS.xlSx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -613,6 +613,46 @@
         </is>
       </c>
       <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>uuuu</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>t4y</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>5tyt545y@oi</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>yy5yt554</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>trrrrrrr</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>trt</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t>2026-05-14</t>
         </is>
